--- a/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
@@ -539,10 +539,10 @@
         <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H10" t="n">
-        <v>6.24</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H11" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.43</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="16">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>18.87</v>
+        <v>17.12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="27">
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>19.06</v>
+        <v>17.29</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H27"/>
+  <dimension ref="A3:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -522,7 +522,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-MORT-CONTRA</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -532,173 +532,173 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mortero de cemento y arena para contrapiso y capas de nivelación de piso.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09</v>
+        <v>0.225</v>
       </c>
       <c r="H10" t="n">
-        <v>4.32</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-CEMENTO</t>
+          <t>MT-ARENA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Cemento Portland gris tipo I, en saco.</t>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0.0504</v>
       </c>
       <c r="G11" t="n">
-        <v>0.225</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.68</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-JUN-CG2</t>
+          <t>MT-AGUA-OBRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mortero de juntas cementoso tipo CG2, de absorción reducida y resistencia elevada a la abrasión, en el color elegido.</t>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de cemento y arena.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.96</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT-CONS-PULIDO</t>
+          <t>MT-JUN-CG2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Consumibles de pulido y abrillantado: discos diamantados, abrasivos y cristalizador.</t>
+          <t>Mortero de juntas cementoso tipo CG2, de absorción reducida y resistencia elevada a la abrasión, en el color elegido.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.52</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>MT-CONS-PULIDO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Consumibles de pulido y abrillantado: discos diamantados, abrasivos y cristalizador.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>MT-SELLA-PIEDRA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Sellador hidrofugante y antimanchas para piedra natural y porcelanato poroso.</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>0.1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" t="n">
         <v>12</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="F15" s="1" t="inlineStr">
+    <row r="16">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="H16" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MQ-MEZCL</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Mezcladora de concreto y mortero de 1 saco, incluida amortización y combustible.</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MQ-PULIDORA</t>
+          <t>MQ-MEZCL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -708,172 +708,198 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Pulidora y abrillantadora de piedra natural con aporte de agua.</t>
+          <t>Mezcladora de concreto y mortero de 1 saco, incluida amortización y combustible.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.26</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>MQ-PULIDORA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Pulidora y abrillantadora de piedra natural con aporte de agua.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>MQ-CORT-AGUA</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Cortadora eléctrica de banco con disco de diamante y refrigeración por agua, incluida amortización y consumo.</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>0.09</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>3.2</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>0.29</v>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>1.77</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MO-OF1-SOL</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª solador.</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>MO-OF1-SOL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª solador.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>0.52</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>3.5</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>1.82</v>
       </c>
     </row>
-    <row r="24">
-      <c r="F24" s="1" t="inlineStr">
+    <row r="25">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>5.67</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="D26" t="inlineStr">
+    <row r="27">
+      <c r="D27" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="G27" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.17</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="5" t="n">
-        <v>17.29</v>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n">
+        <v>16.8</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de piedra natural y granito</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-040.xlsx
@@ -810,7 +810,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F23" t="n">
